--- a/artfynd/A 49676-2024 artfynd.xlsx
+++ b/artfynd/A 49676-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130232730</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130232721</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130232733</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,6 +1001,107 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130255246</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>504141</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6691611</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49676-2024 artfynd.xlsx
+++ b/artfynd/A 49676-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130232730</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130232721</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130255246</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49676-2024 artfynd.xlsx
+++ b/artfynd/A 49676-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130232730</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130232721</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130232733</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130255246</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49676-2024 artfynd.xlsx
+++ b/artfynd/A 49676-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130232730</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130232721</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130232733</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130255246</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49676-2024 artfynd.xlsx
+++ b/artfynd/A 49676-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>130255246</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49676-2024 artfynd.xlsx
+++ b/artfynd/A 49676-2024 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>131078252</v>
       </c>
       <c r="B6" t="n">
-        <v>57064</v>
+        <v>57066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49676-2024 artfynd.xlsx
+++ b/artfynd/A 49676-2024 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>131078252</v>
       </c>
       <c r="B6" t="n">
-        <v>57066</v>
+        <v>57067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49676-2024 artfynd.xlsx
+++ b/artfynd/A 49676-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130232730</v>
+        <v>130233568</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lördag, Dlr</t>
+          <t>Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504160</v>
+        <v>504129</v>
       </c>
       <c r="R2" t="n">
-        <v>6691770</v>
+        <v>6691806</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +756,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +766,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,18 +775,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,11 +797,11 @@
         <v>130232721</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -889,43 +901,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130232733</v>
+        <v>130232722</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lördag, Dlr</t>
@@ -967,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,14 +1008,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130255246</v>
+        <v>130232735</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1033,22 +1037,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmyran, Dlr</t>
+          <t>Lördag, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504141</v>
+        <v>504104</v>
       </c>
       <c r="R5" t="n">
-        <v>6691611</v>
+        <v>6691565</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,102 +1076,87 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131078252</v>
+        <v>130232739</v>
       </c>
       <c r="B6" t="n">
-        <v>57067</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långmyran, Dlr</t>
+          <t>Lördag, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504140</v>
+        <v>504089</v>
       </c>
       <c r="R6" t="n">
-        <v>6691587</v>
+        <v>6691612</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,17 +1180,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Jag lockar fram tuppen med järppipa efter att ha stött den under skidåkning.</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,15 +1210,357 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130255246</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>504141</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6691611</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130232733</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lördag, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>504160</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6691770</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131078252</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>504140</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6691587</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Jag lockar fram tuppen med järppipa efter att ha stött den under skidåkning.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Tobias Hellberg</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Tobias Hellberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
